--- a/public/plantillas/Makro/offer_template DE.xlsx
+++ b/public/plantillas/Makro/offer_template DE.xlsx
@@ -1832,25 +1832,404 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G30" s="4"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641312</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4">
+        <v>109.24</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>107</v>
+      </c>
+      <c r="O30">
+        <v>105</v>
+      </c>
+      <c r="P30">
+        <v>103</v>
+      </c>
+      <c r="Q30">
+        <v>101</v>
+      </c>
+      <c r="V30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G31" s="4"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641336</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4">
+        <v>109.24</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="L31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>107</v>
+      </c>
+      <c r="O31">
+        <v>105</v>
+      </c>
+      <c r="P31">
+        <v>103</v>
+      </c>
+      <c r="Q31">
+        <v>101</v>
+      </c>
+      <c r="V31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641329</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5">
+        <v>109.24</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>107</v>
+      </c>
+      <c r="O32">
+        <v>105</v>
+      </c>
+      <c r="P32">
+        <v>103</v>
+      </c>
+      <c r="Q32">
+        <v>101</v>
+      </c>
+      <c r="V32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="33" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G33" s="3"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641343</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>109.24</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="L33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>107</v>
+      </c>
+      <c r="O33">
+        <v>105</v>
+      </c>
+      <c r="P33">
+        <v>103</v>
+      </c>
+      <c r="Q33">
+        <v>101</v>
+      </c>
+      <c r="V33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G34" s="3"/>
+      <c r="A34" s="2">
+        <v>8437027641350</v>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>146.22</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>144</v>
+      </c>
+      <c r="O34">
+        <v>142</v>
+      </c>
+      <c r="P34">
+        <v>140</v>
+      </c>
+      <c r="Q34">
+        <v>138</v>
+      </c>
+      <c r="V34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="35" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G35" s="3"/>
+      <c r="A35" s="2">
+        <v>8437027641374</v>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>146.22</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="L35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>144</v>
+      </c>
+      <c r="O35">
+        <v>142</v>
+      </c>
+      <c r="P35">
+        <v>140</v>
+      </c>
+      <c r="Q35">
+        <v>138</v>
+      </c>
+      <c r="V35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="36" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G36" s="3"/>
+      <c r="A36" s="2">
+        <v>8437027641367</v>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3">
+        <v>146.22</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="L36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>144</v>
+      </c>
+      <c r="O36">
+        <v>142</v>
+      </c>
+      <c r="P36">
+        <v>140</v>
+      </c>
+      <c r="Q36">
+        <v>138</v>
+      </c>
+      <c r="V36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="37" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G37" s="3"/>
+      <c r="A37" s="2">
+        <v>8437027641381</v>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3">
+        <v>146.22</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="L37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>144</v>
+      </c>
+      <c r="O37">
+        <v>142</v>
+      </c>
+      <c r="P37">
+        <v>140</v>
+      </c>
+      <c r="Q37">
+        <v>138</v>
+      </c>
+      <c r="V37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="38" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="G38" s="3"/>

--- a/public/plantillas/Makro/offer_template DE.xlsx
+++ b/public/plantillas/Makro/offer_template DE.xlsx
@@ -2232,34 +2232,514 @@
       </c>
     </row>
     <row r="38" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G38" s="3"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641534</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3">
+        <v>100.84</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>97.81</v>
+      </c>
+      <c r="O38">
+        <v>96.81</v>
+      </c>
+      <c r="P38">
+        <v>95.8</v>
+      </c>
+      <c r="Q38">
+        <v>94.79</v>
+      </c>
+      <c r="V38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="39" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G39" s="3"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641480</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>100</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="L39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N39">
+        <v>97</v>
+      </c>
+      <c r="O39">
+        <v>96</v>
+      </c>
+      <c r="P39">
+        <v>95</v>
+      </c>
+      <c r="Q39">
+        <v>94</v>
+      </c>
+      <c r="V39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="40" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G40" s="3"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641497</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
+        <v>252.1</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
+      <c r="L40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>244.54</v>
+      </c>
+      <c r="O40">
+        <v>242.02</v>
+      </c>
+      <c r="P40">
+        <v>239.49</v>
+      </c>
+      <c r="Q40">
+        <v>236.97</v>
+      </c>
+      <c r="V40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="41" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G41" s="3"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641442</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>252.1</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="L41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>244.54</v>
+      </c>
+      <c r="O41">
+        <v>242.02</v>
+      </c>
+      <c r="P41">
+        <v>239.49</v>
+      </c>
+      <c r="Q41">
+        <v>236.97</v>
+      </c>
+      <c r="V41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="42" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G42" s="3"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641503</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>150.42</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="L42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>145.91</v>
+      </c>
+      <c r="O42">
+        <v>144.4</v>
+      </c>
+      <c r="P42">
+        <v>142.9</v>
+      </c>
+      <c r="Q42">
+        <v>141.39</v>
+      </c>
+      <c r="V42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="43" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G43" s="3"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641459</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>150.42</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="L43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>145.91</v>
+      </c>
+      <c r="O43">
+        <v>144.4</v>
+      </c>
+      <c r="P43">
+        <v>142.9</v>
+      </c>
+      <c r="Q43">
+        <v>141.39</v>
+      </c>
+      <c r="V43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="44" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G44" s="3"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641510</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>167.23</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="L44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N44">
+        <v>162.21</v>
+      </c>
+      <c r="O44">
+        <v>160.54</v>
+      </c>
+      <c r="P44">
+        <v>158.87</v>
+      </c>
+      <c r="Q44">
+        <v>157.2</v>
+      </c>
+      <c r="V44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="45" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G45" s="3"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641466</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>168.07</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+      <c r="L45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N45">
+        <v>163.03</v>
+      </c>
+      <c r="O45">
+        <v>161.35</v>
+      </c>
+      <c r="P45">
+        <v>159.67</v>
+      </c>
+      <c r="Q45">
+        <v>157.99</v>
+      </c>
+      <c r="V45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="46" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G46" s="3"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641527</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3">
+        <v>234.45</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>2</v>
+      </c>
+      <c r="L46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N46">
+        <v>227.42</v>
+      </c>
+      <c r="O46">
+        <v>225.07</v>
+      </c>
+      <c r="P46">
+        <v>222.73</v>
+      </c>
+      <c r="Q46">
+        <v>220.38</v>
+      </c>
+      <c r="V46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="47" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G47" s="3"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641473</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>234.45</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
+      </c>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE_MAIN</t>
+        </is>
+      </c>
+      <c r="M47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N47">
+        <v>227.42</v>
+      </c>
+      <c r="O47">
+        <v>225.07</v>
+      </c>
+      <c r="P47">
+        <v>222.73</v>
+      </c>
+      <c r="Q47">
+        <v>220.38</v>
+      </c>
+      <c r="V47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="48" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="G48" s="3"/>
